--- a/EDA/aml_data_dictionary_updated.xlsx
+++ b/EDA/aml_data_dictionary_updated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc4bd521ffc22738/Desktop/Freelancing/AIGEN/smartsentry_aml_model/EDA/Updated Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc4bd521ffc22738/Desktop/Freelancing/AIGEN/smartsentry_aml_model/EDA/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CFAA0AA9-EADD-4390-9162-A8E07068B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
